--- a/Simulation_of_Multiple_Scenarios/Plot_data_and_code/Economic Breakeven Point/data/sensitivity/commercial/hydrogen.xlsx
+++ b/Simulation_of_Multiple_Scenarios/Plot_data_and_code/Economic Breakeven Point/data/sensitivity/commercial/hydrogen.xlsx
@@ -182,10 +182,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="MS PGothic"/>
+        <a:font script="Hang" typeface="Malgun Gothic"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -216,10 +216,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="MS PGothic"/>
+        <a:font script="Hang" typeface="Malgun Gothic"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
